--- a/jogos_2025-03-17.xlsx
+++ b/jogos_2025-03-17.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.68</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63</v>
+        <v>3.26</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.35</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45733.41666666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.06</v>
+        <v>2.68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.13</v>
+        <v>2.63</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.5</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['28', '53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45733.41666666666</v>
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="N5" t="n">
-        <v>6.9</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>1.5</v>
@@ -1086,7 +1086,7 @@
         <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
         <v>1.4</v>
@@ -1107,32 +1107,32 @@
         <v>1.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['28', '53']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45733.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>2.09</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>3.54</v>
       </c>
       <c r="O8" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.5</v>
+        <v>4.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['8', '31', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.97</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45733.58333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.72</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
         <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
         <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45733.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,65 +1959,65 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.98</v>
+        <v>3.34</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['8', '31', '68']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45733.58333333334</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>13</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['48', '55', '90', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '58', '87']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.18</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.22</v>
+        <v>3.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45733.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>13</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['48', '55', '90', '90+2']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>3.18</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45733.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['14', '47']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['6', '57']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.35</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['3', '58', '87']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45733.6875</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.86</v>
+        <v>2.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45733.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="M20" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
-        <v>3.12</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['15', '25', '31']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45733.6875</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>3.12</v>
       </c>
       <c r="O21" t="n">
         <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
         <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['14', '47']</t>
+          <t>['15', '25', '31']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['6', '57']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45733.6875</v>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3249,55 +3249,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="N22" t="n">
-        <v>3.51</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
         <v>2</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45733.75</v>
@@ -3352,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>3.99</v>
+        <v>3.51</v>
       </c>
       <c r="O23" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45733.75</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="N33" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S33" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X33" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['44', '87']</t>
+          <t>['27', '68']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI33" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45733.88541666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="M34" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="O34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.25</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.57</v>
       </c>
-      <c r="S34" t="n">
+      <c r="AD34" t="n">
         <v>2.25</v>
       </c>
-      <c r="T34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['27', '68']</t>
+          <t>['44', '87']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AI34" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45733.88541666666</v>
